--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486331_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486331_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7115</v>
+        <v>7.3494</v>
       </c>
       <c r="E2" t="n">
-        <v>9.316800000000001</v>
+        <v>9.677300000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.6053</v>
+        <v>-2.3279</v>
       </c>
       <c r="G2" t="n">
         <v>5.7135</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.6116</v>
+        <v>-0.9737</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.3929</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.8581</v>
+        <v>-0.5807</v>
       </c>
       <c r="V2" t="n">
         <v>1.3045</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. VILA SOLEY</t>
+          <t>M. JACKSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9157</v>
+        <v>2.6906</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0732</v>
+        <v>2.8939</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.1575</v>
+        <v>-0.2032</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9684</v>
+        <v>3.0647</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3253</v>
+        <v>-2.1412</v>
       </c>
       <c r="I3" t="n">
-        <v>1.6431</v>
+        <v>5.2059</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6381</v>
+        <v>4.2013</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5726</v>
+        <v>-0.4285</v>
       </c>
       <c r="L3" t="n">
-        <v>2.0655</v>
+        <v>4.6298</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6696</v>
+        <v>-1.1366</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2473</v>
+        <v>-1.7127</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4224</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6525</v>
+        <v>0.435</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R3" t="n">
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4046</v>
+        <v>-0.8316</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0898</v>
+        <v>-0.2199</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6852</v>
+        <v>-0.6117</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1952</v>
+        <v>0.0225</v>
       </c>
       <c r="W3" t="n">
-        <v>1.5204</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.3252</v>
+        <v>0.0225</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2485</v>
+        <v>2.1928</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3471</v>
+        <v>1.2605</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9015</v>
+        <v>0.9323</v>
       </c>
       <c r="G4" t="n">
         <v>1.0447</v>
@@ -766,13 +766,13 @@
         <v>0.87</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0359</v>
+        <v>-0.0916</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1971</v>
+        <v>0.1106</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.233</v>
+        <v>-0.2022</v>
       </c>
       <c r="V4" t="n">
         <v>0.3698</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. JACKSON</t>
+          <t>R. VILA SOLEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8146</v>
+        <v>1.8031</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0178</v>
+        <v>3.7141</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2032</v>
+        <v>-1.9109</v>
       </c>
       <c r="G5" t="n">
-        <v>3.0647</v>
+        <v>1.9684</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.1412</v>
+        <v>0.3253</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2059</v>
+        <v>1.6431</v>
       </c>
       <c r="J5" t="n">
-        <v>4.2013</v>
+        <v>3.6381</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4285</v>
+        <v>1.5726</v>
       </c>
       <c r="L5" t="n">
-        <v>4.6298</v>
+        <v>2.0655</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1366</v>
+        <v>-1.6696</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7127</v>
+        <v>-1.2473</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.4224</v>
       </c>
       <c r="P5" t="n">
-        <v>0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R5" t="n">
         <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7076</v>
+        <v>0.292</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.0959</v>
+        <v>0.7306</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6117</v>
+        <v>-0.4386</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0225</v>
+        <v>0.1952</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.5204</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0225</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BROWN-FERGUSON</t>
+          <t>J. ZIDEK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6491</v>
+        <v>0.3081</v>
       </c>
       <c r="E6" t="n">
-        <v>1.379</v>
+        <v>0.1918</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.73</v>
+        <v>0.1163</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2585</v>
+        <v>-0.9915</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2585</v>
+        <v>-0.2768</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.7148</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8395</v>
+        <v>0.3218</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8395</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.6303</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.581</v>
+        <v>-1.3134</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.581</v>
+        <v>-1.2289</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3906</v>
+        <v>-0.5699</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5396</v>
+        <v>-0.3677</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.149</v>
+        <v>-0.2022</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.8695</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. ZIDEK</t>
+          <t>J. BROWN-FERGUSON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.097</v>
+        <v>0.202</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0115</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08550000000000001</v>
+        <v>-0.73</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9915</v>
+        <v>0.2585</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.2768</v>
+        <v>0.2585</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7148</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3218</v>
+        <v>0.8395</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9520999999999999</v>
+        <v>0.8395</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6303</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3134</v>
+        <v>-0.581</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2289</v>
+        <v>-0.581</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.781</v>
+        <v>-0.0565</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.548</v>
+        <v>0.0925</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.233</v>
+        <v>-0.149</v>
       </c>
       <c r="V7" t="n">
-        <v>1.8695</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0861</v>
+        <v>-1.2555</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6424</v>
+        <v>-0.0583</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4437</v>
+        <v>-1.1971</v>
       </c>
       <c r="G8" t="n">
         <v>0.1463</v>
@@ -1078,13 +1078,13 @@
         <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8426</v>
+        <v>-0.012</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.411</v>
+        <v>0.173</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4317</v>
+        <v>-0.1851</v>
       </c>
       <c r="V8" t="n">
         <v>-2.0422</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.8943</v>
+        <v>-3.581</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9501</v>
+        <v>-2.3286</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9442</v>
+        <v>-1.2524</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5119</v>
@@ -1156,13 +1156,13 @@
         <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2055</v>
+        <v>-0.4813</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1286</v>
+        <v>-0.2499</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0769</v>
+        <v>-0.2313</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1952</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.9003</v>
+        <v>-5.8095</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.2329</v>
+        <v>-6.6488</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3325</v>
+        <v>0.8394</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5094</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3444</v>
+        <v>-0.2536</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.1009</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3405</v>
+        <v>-0.1526</v>
       </c>
       <c r="V10" t="n">
         <v>0.4336</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4973</v>
+        <v>-6.1368</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0215</v>
+        <v>-2.661</v>
       </c>
       <c r="F11" t="n">
         <v>-3.4758</v>
@@ -1312,10 +1312,10 @@
         <v>1.7401</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1921</v>
+        <v>-0.8316</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.3245</v>
       </c>
       <c r="U11" t="n">
         <v>-0.5071</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.022600000000001</v>
+        <v>-7.3654</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.0551</v>
+        <v>-3.5828</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9675</v>
+        <v>-3.7825</v>
       </c>
       <c r="G12" t="n">
         <v>-2.7023</v>
@@ -1390,13 +1390,13 @@
         <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.5603</v>
+        <v>-0.9031</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6850000000000001</v>
+        <v>-0.2127</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8753</v>
+        <v>-0.6904</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2375</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.840199999999999</v>
+        <v>-9.8325</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.4661</v>
+        <v>-6.2425</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.3742</v>
+        <v>-3.5899</v>
       </c>
       <c r="G13" t="n">
         <v>-5.0198</v>
@@ -1468,13 +1468,13 @@
         <v>0.87</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1679</v>
+        <v>-0.1601</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.411</v>
+        <v>-0.1875</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2431</v>
+        <v>0.0273</v>
       </c>
       <c r="V13" t="n">
         <v>-2.2599</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-20.8044</v>
+        <v>-19.4347</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.2227</v>
+        <v>-2.852400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.5819</v>
+        <v>-16.5817</v>
       </c>
       <c r="G14" t="n">
         <v>-3.279800000000001</v>
@@ -1546,16 +1546,16 @@
         <v>13.0502</v>
       </c>
       <c r="S14" t="n">
-        <v>-6.2427</v>
+        <v>-4.872999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.3193</v>
+        <v>-0.9492999999999999</v>
       </c>
       <c r="U14" t="n">
         <v>-3.9236</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.756499999999999</v>
+        <v>-4.7565</v>
       </c>
       <c r="W14" t="n">
         <v>7.037100000000001</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. OKANU</t>
+          <t>I. VAZQUEZ PEREZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.97</v>
+        <v>6.2407</v>
       </c>
       <c r="E15" t="n">
-        <v>6.4062</v>
+        <v>5.4972</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5638</v>
+        <v>0.7435</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0275</v>
+        <v>2.7739</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3336</v>
+        <v>3.7381</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.3061</v>
+        <v>-0.9641999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3512</v>
+        <v>4.9247</v>
       </c>
       <c r="K15" t="n">
-        <v>3.2365</v>
+        <v>3.872</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1147</v>
+        <v>1.0527</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3237</v>
+        <v>-2.1508</v>
       </c>
       <c r="N15" t="n">
-        <v>0.09710000000000001</v>
+        <v>-0.1339</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4208</v>
+        <v>-2.0169</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>2.1751</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>2.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>3.2061</v>
+        <v>1.0965</v>
       </c>
       <c r="T15" t="n">
-        <v>2.3638</v>
+        <v>0.3773</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8424</v>
+        <v>0.7192</v>
       </c>
       <c r="V15" t="n">
-        <v>1.7363</v>
+        <v>0.1952</v>
       </c>
       <c r="W15" t="n">
-        <v>2.8663</v>
+        <v>0.1952</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>I. VAZQUEZ PEREZ</t>
+          <t>R. DIAS MARQUES LISBOA SANTOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.1906</v>
+        <v>5.3271</v>
       </c>
       <c r="E16" t="n">
-        <v>5.3855</v>
+        <v>4.0481</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8051</v>
+        <v>1.279</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7739</v>
+        <v>4.2466</v>
       </c>
       <c r="H16" t="n">
-        <v>3.7381</v>
+        <v>4.045</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.9641999999999999</v>
+        <v>0.2016</v>
       </c>
       <c r="J16" t="n">
-        <v>4.9247</v>
+        <v>4.5208</v>
       </c>
       <c r="K16" t="n">
-        <v>3.872</v>
+        <v>3.8324</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0527</v>
+        <v>0.6885</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1508</v>
+        <v>-0.2742</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1339</v>
+        <v>0.2127</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.0169</v>
+        <v>-0.4869</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R16" t="n">
-        <v>2.1751</v>
+        <v>1.9576</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0464</v>
+        <v>-0.137</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2656</v>
+        <v>0.0721</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7809</v>
+        <v>-0.2091</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1952</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1952</v>
+        <v>0.7602</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. DIAS MARQUES LISBOA SANTOS</t>
+          <t>C. OKANU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3098</v>
+        <v>5.0971</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1541</v>
+        <v>4.8416</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1557</v>
+        <v>0.2555</v>
       </c>
       <c r="G17" t="n">
-        <v>4.2466</v>
+        <v>2.0275</v>
       </c>
       <c r="H17" t="n">
-        <v>4.045</v>
+        <v>3.3336</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2016</v>
+        <v>-1.3061</v>
       </c>
       <c r="J17" t="n">
-        <v>4.5208</v>
+        <v>3.3512</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8324</v>
+        <v>3.2365</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6885</v>
+        <v>0.1147</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2742</v>
+        <v>-1.3237</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2127</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4869</v>
+        <v>-1.4208</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6525</v>
+        <v>-0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.305</v>
+        <v>-2.1751</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.1543</v>
+        <v>1.3333</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.822</v>
+        <v>0.7991</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3324</v>
+        <v>0.5341</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5649999999999999</v>
+        <v>1.7363</v>
       </c>
       <c r="W17" t="n">
-        <v>0.7602</v>
+        <v>2.8663</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.0061</v>
+        <v>4.1545</v>
       </c>
       <c r="E18" t="n">
-        <v>4.5915</v>
+        <v>5.709</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5853</v>
+        <v>-1.5545</v>
       </c>
       <c r="G18" t="n">
         <v>-2.8991</v>
@@ -1858,13 +1858,13 @@
         <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1595</v>
+        <v>-0.0111</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0274</v>
+        <v>0.0901</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1321</v>
+        <v>-0.1013</v>
       </c>
       <c r="V18" t="n">
         <v>4.8897</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.9315</v>
+        <v>2.7889</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3759</v>
+        <v>2.2641</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5556</v>
+        <v>0.5248</v>
       </c>
       <c r="G19" t="n">
         <v>2.7428</v>
@@ -1936,13 +1936,13 @@
         <v>1.5225</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6884</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3341</v>
+        <v>0.2223</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3544</v>
+        <v>0.3235</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9347</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. GILL</t>
+          <t>S. MC DONNELL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7955</v>
+        <v>1.8154</v>
       </c>
       <c r="E20" t="n">
-        <v>1.7776</v>
+        <v>-0.9615</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0179</v>
+        <v>2.7768</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1992</v>
+        <v>-3.0165</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1004</v>
+        <v>-0.0427</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0988</v>
+        <v>-2.9739</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6201</v>
+        <v>-1.5773</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0302</v>
+        <v>-0.4713</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6502</v>
+        <v>-1.106</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4208</v>
+        <v>-1.4392</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1306</v>
+        <v>0.4286</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5514</v>
+        <v>-1.8679</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2175</v>
+        <v>3.2626</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.305</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5225</v>
+        <v>3.2626</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3787</v>
+        <v>0.8298</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9421</v>
+        <v>0.4206</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4366</v>
+        <v>0.4092</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.7395</v>
       </c>
       <c r="W20" t="n">
-        <v>1.5204</v>
+        <v>0.1952</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.5204</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. MC DONNELL</t>
+          <t>R. GILL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4069</v>
+        <v>1.1327</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.185</v>
+        <v>1.3306</v>
       </c>
       <c r="F21" t="n">
-        <v>2.5919</v>
+        <v>-0.1979</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0165</v>
+        <v>0.1992</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0427</v>
+        <v>0.1004</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9739</v>
+        <v>0.0988</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.5773</v>
+        <v>0.6201</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4713</v>
+        <v>-0.0302</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.106</v>
+        <v>0.6502</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4392</v>
+        <v>-0.4208</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4286</v>
+        <v>0.1306</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.8679</v>
+        <v>-0.5514</v>
       </c>
       <c r="P21" t="n">
-        <v>3.2626</v>
+        <v>0.2175</v>
       </c>
       <c r="Q21" t="n">
+        <v>-1.305</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5225</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.7159</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.4951</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.2208</v>
+      </c>
+      <c r="V21" t="n">
         <v>0</v>
       </c>
-      <c r="R21" t="n">
-        <v>3.2626</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0.4213</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0.1971</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0.2242</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.7395</v>
-      </c>
       <c r="W21" t="n">
-        <v>0.1952</v>
+        <v>1.5204</v>
       </c>
       <c r="X21" t="n">
-        <v>0.5443</v>
+        <v>-1.5204</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.037</v>
+        <v>0.4532</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7537</v>
+        <v>-0.3066</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7907</v>
+        <v>0.7598</v>
       </c>
       <c r="G22" t="n">
         <v>-0.371</v>
@@ -2170,13 +2170,13 @@
         <v>1.9576</v>
       </c>
       <c r="S22" t="n">
-        <v>0.495</v>
+        <v>0.9112</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0601</v>
+        <v>0.5071</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4349</v>
+        <v>0.4041</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7395</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2948</v>
+        <v>-1.5376</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.9986</v>
+        <v>-1.3338</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2962</v>
+        <v>-0.2037</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2658</v>
@@ -2248,13 +2248,13 @@
         <v>0.2175</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1662</v>
+        <v>-0.0766</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4026</v>
+        <v>0.0673</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2364</v>
+        <v>-0.1439</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1952</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. HUGUET CARRASCO</t>
+          <t>K. SMITH</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2372</v>
+        <v>-2.2377</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7659</v>
+        <v>-2.5174</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4713</v>
+        <v>0.2798</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.3368</v>
+        <v>-0.8209</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2523</v>
+        <v>-0.8576</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.08450000000000001</v>
+        <v>0.0366</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1127</v>
+        <v>0.1203</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1127</v>
+        <v>-1.1037</v>
       </c>
       <c r="L24" t="n">
+        <v>1.224</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.9412</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.2461</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-1.1873</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.9576</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-3.2626</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.305</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.6249</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.1111</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.1952</v>
+      </c>
+      <c r="W24" t="n">
         <v>0</v>
       </c>
-      <c r="M24" t="n">
-        <v>-0.4495</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-0.365</v>
-      </c>
-      <c r="O24" t="n">
-        <v>-0.08450000000000001</v>
-      </c>
-      <c r="P24" t="n">
-        <v>-1.0875</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-2.1751</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.0875</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0.4916</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0.4711</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.0205</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-1.3045</v>
-      </c>
-      <c r="W24" t="n">
-        <v>-0.1745</v>
-      </c>
       <c r="X24" t="n">
-        <v>-1.13</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>K. SMITH</t>
+          <t>S. HUGUET CARRASCO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.3109</v>
+        <v>-2.4299</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4057</v>
+        <v>-1.9894</v>
       </c>
       <c r="F25" t="n">
-        <v>0.0948</v>
+        <v>-0.4405</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.8209</v>
+        <v>-0.3368</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.8576</v>
+        <v>-0.2523</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0366</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1203</v>
+        <v>0.1127</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.1037</v>
+        <v>0.1127</v>
       </c>
       <c r="L25" t="n">
-        <v>1.224</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.9412</v>
+        <v>-0.4495</v>
       </c>
       <c r="N25" t="n">
-        <v>0.2461</v>
+        <v>-0.365</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.1873</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-1.9576</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.2626</v>
+        <v>-2.1751</v>
       </c>
       <c r="R25" t="n">
-        <v>1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6629</v>
+        <v>0.2989</v>
       </c>
       <c r="T25" t="n">
-        <v>0.7367</v>
+        <v>0.2476</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0738</v>
+        <v>0.0514</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.1952</v>
+        <v>-1.3045</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.1745</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.1952</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="26">
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>20.8045</v>
+        <v>20.8044</v>
       </c>
       <c r="E26" t="n">
         <v>16.5819</v>
       </c>
       <c r="F26" t="n">
-        <v>4.222700000000001</v>
+        <v>4.2226</v>
       </c>
       <c r="G26" t="n">
-        <v>3.279899999999998</v>
+        <v>3.2799</v>
       </c>
       <c r="H26" t="n">
         <v>14.4319</v>
@@ -2461,7 +2461,7 @@
         <v>13.2934</v>
       </c>
       <c r="L26" t="n">
-        <v>0.6217</v>
+        <v>0.6217000000000003</v>
       </c>
       <c r="M26" t="n">
         <v>-10.635</v>
@@ -2473,7 +2473,7 @@
         <v>-11.7738</v>
       </c>
       <c r="P26" t="n">
-        <v>6.525199999999999</v>
+        <v>6.5252</v>
       </c>
       <c r="Q26" t="n">
         <v>-13.0503</v>
@@ -2482,13 +2482,13 @@
         <v>19.5756</v>
       </c>
       <c r="S26" t="n">
-        <v>6.242800000000001</v>
+        <v>6.242799999999999</v>
       </c>
       <c r="T26" t="n">
-        <v>3.9238</v>
+        <v>3.923499999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>2.3192</v>
+        <v>2.319100000000001</v>
       </c>
       <c r="V26" t="n">
         <v>4.756600000000001</v>
